--- a/Section_&_Thickness_change_over_cost.xlsx
+++ b/Section_&_Thickness_change_over_cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rpgnet-my.sharepoint.com/personal/sankuria_kecrpg_com/Documents/Desktop/Vinar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rolling-plan-optimizer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{759C099D-C368-47AF-9AE7-F597B6CE3CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EC0E447-27FF-4682-B80D-3EFD17E2C4C5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8C1853-C356-4D49-9522-5E56E71B7311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Section Roll Changeover Time" sheetId="9" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="56">
   <si>
     <t>Section</t>
   </si>
@@ -167,12 +167,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>6-8 Hr</t>
-  </si>
-  <si>
-    <t>8-12 Hr</t>
-  </si>
-  <si>
     <t>Manpower cost for section changes</t>
   </si>
   <si>
@@ -219,12 +213,6 @@
   </si>
   <si>
     <t>Please note in some section the thickness time may vary to up to 45 minutes.</t>
-  </si>
-  <si>
-    <t>8-12 Hrs</t>
-  </si>
-  <si>
-    <t>6-8 Hrs</t>
   </si>
 </sst>
 </file>
@@ -472,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -537,9 +525,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -594,6 +579,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -988,461 +985,461 @@
       <c r="A2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="7"/>
+      <c r="B2" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="43">
+        <v>7</v>
+      </c>
+      <c r="D2" s="43">
+        <v>7</v>
+      </c>
+      <c r="E2" s="43">
+        <v>7</v>
+      </c>
+      <c r="F2" s="43">
+        <v>7</v>
+      </c>
+      <c r="G2" s="43">
+        <v>10</v>
+      </c>
+      <c r="H2" s="43">
+        <v>10</v>
+      </c>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="44"/>
     </row>
     <row r="3" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="7"/>
+      <c r="B3" s="43">
+        <v>7</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="43">
+        <v>7</v>
+      </c>
+      <c r="E3" s="43">
+        <v>7</v>
+      </c>
+      <c r="F3" s="43">
+        <v>7</v>
+      </c>
+      <c r="G3" s="43">
+        <v>10</v>
+      </c>
+      <c r="H3" s="43">
+        <v>10</v>
+      </c>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="44"/>
     </row>
     <row r="4" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="7"/>
+      <c r="B4" s="43">
+        <v>7</v>
+      </c>
+      <c r="C4" s="43">
+        <v>7</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="43">
+        <v>7</v>
+      </c>
+      <c r="F4" s="43">
+        <v>7</v>
+      </c>
+      <c r="G4" s="43">
+        <v>10</v>
+      </c>
+      <c r="H4" s="43">
+        <v>10</v>
+      </c>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="44"/>
     </row>
     <row r="5" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="7"/>
+      <c r="B5" s="43">
+        <v>7</v>
+      </c>
+      <c r="C5" s="43">
+        <v>7</v>
+      </c>
+      <c r="D5" s="43">
+        <v>7</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="43">
+        <v>7</v>
+      </c>
+      <c r="G5" s="43">
+        <v>10</v>
+      </c>
+      <c r="H5" s="43">
+        <v>10</v>
+      </c>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="44"/>
     </row>
     <row r="6" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="7"/>
+      <c r="B6" s="43">
+        <v>7</v>
+      </c>
+      <c r="C6" s="43">
+        <v>7</v>
+      </c>
+      <c r="D6" s="43">
+        <v>7</v>
+      </c>
+      <c r="E6" s="43">
+        <v>7</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="43">
+        <v>7</v>
+      </c>
+      <c r="H6" s="43">
+        <v>10</v>
+      </c>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="44"/>
     </row>
     <row r="7" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="7"/>
+      <c r="B7" s="43">
+        <v>10</v>
+      </c>
+      <c r="C7" s="43">
+        <v>10</v>
+      </c>
+      <c r="D7" s="43">
+        <v>10</v>
+      </c>
+      <c r="E7" s="43">
+        <v>7</v>
+      </c>
+      <c r="F7" s="43">
+        <v>7</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="43">
+        <v>7</v>
+      </c>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="44"/>
     </row>
     <row r="8" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="7"/>
+      <c r="B8" s="43">
+        <v>10</v>
+      </c>
+      <c r="C8" s="43">
+        <v>10</v>
+      </c>
+      <c r="D8" s="43">
+        <v>10</v>
+      </c>
+      <c r="E8" s="43">
+        <v>10</v>
+      </c>
+      <c r="F8" s="43">
+        <v>7</v>
+      </c>
+      <c r="G8" s="43">
+        <v>7</v>
+      </c>
+      <c r="H8" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="44"/>
     </row>
     <row r="9" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>58</v>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="43">
+        <v>7</v>
+      </c>
+      <c r="K9" s="43">
+        <v>7</v>
+      </c>
+      <c r="L9" s="43">
+        <v>10</v>
+      </c>
+      <c r="M9" s="43">
+        <v>10</v>
+      </c>
+      <c r="N9" s="43">
+        <v>10</v>
+      </c>
+      <c r="O9" s="43">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>58</v>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43">
+        <v>7</v>
+      </c>
+      <c r="J10" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" s="43">
+        <v>7</v>
+      </c>
+      <c r="L10" s="43">
+        <v>10</v>
+      </c>
+      <c r="M10" s="43">
+        <v>10</v>
+      </c>
+      <c r="N10" s="43">
+        <v>10</v>
+      </c>
+      <c r="O10" s="43">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>58</v>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43">
+        <v>7</v>
+      </c>
+      <c r="J11" s="43">
+        <v>7</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="L11" s="43">
+        <v>10</v>
+      </c>
+      <c r="M11" s="43">
+        <v>10</v>
+      </c>
+      <c r="N11" s="43">
+        <v>10</v>
+      </c>
+      <c r="O11" s="43">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>58</v>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43">
+        <v>10</v>
+      </c>
+      <c r="J12" s="43">
+        <v>10</v>
+      </c>
+      <c r="K12" s="43">
+        <v>10</v>
+      </c>
+      <c r="L12" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="M12" s="43">
+        <v>10</v>
+      </c>
+      <c r="N12" s="43">
+        <v>10</v>
+      </c>
+      <c r="O12" s="43">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="N13" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>58</v>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43">
+        <v>10</v>
+      </c>
+      <c r="J13" s="43">
+        <v>10</v>
+      </c>
+      <c r="K13" s="43">
+        <v>10</v>
+      </c>
+      <c r="L13" s="43">
+        <v>10</v>
+      </c>
+      <c r="M13" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="N13" s="43">
+        <v>7</v>
+      </c>
+      <c r="O13" s="43">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>58</v>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43">
+        <v>10</v>
+      </c>
+      <c r="J14" s="43">
+        <v>10</v>
+      </c>
+      <c r="K14" s="43">
+        <v>10</v>
+      </c>
+      <c r="L14" s="43">
+        <v>10</v>
+      </c>
+      <c r="M14" s="43">
+        <v>7</v>
+      </c>
+      <c r="N14" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="O14" s="43">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="O15" s="9" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="43">
+        <v>10</v>
+      </c>
+      <c r="J15" s="43">
+        <v>10</v>
+      </c>
+      <c r="K15" s="43">
+        <v>10</v>
+      </c>
+      <c r="L15" s="43">
+        <v>10</v>
+      </c>
+      <c r="M15" s="45">
+        <v>10</v>
+      </c>
+      <c r="N15" s="45">
+        <v>10</v>
+      </c>
+      <c r="O15" s="46" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1469,7 +1466,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1504,16 +1501,16 @@
       <c r="B3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="36">
+      <c r="D3" s="35">
         <v>11</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="35">
         <v>14933</v>
       </c>
     </row>
@@ -1524,10 +1521,10 @@
       <c r="B4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="40"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="17">
@@ -1536,10 +1533,10 @@
       <c r="B5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="40"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="39"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="17">
@@ -1548,10 +1545,10 @@
       <c r="B6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="40"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="39"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="17">
@@ -1560,10 +1557,10 @@
       <c r="B7" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="40"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="39"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="17">
@@ -1572,10 +1569,10 @@
       <c r="B8" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="17">
@@ -1584,14 +1581,14 @@
       <c r="B9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="35">
         <v>3</v>
       </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="36">
+      <c r="E9" s="41"/>
+      <c r="F9" s="35">
         <v>4133</v>
       </c>
     </row>
@@ -1602,10 +1599,10 @@
       <c r="B10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="37"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="17">
@@ -1614,14 +1611,14 @@
       <c r="B11" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="36">
-        <v>2</v>
-      </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="36">
+      <c r="D11" s="35">
+        <v>2</v>
+      </c>
+      <c r="E11" s="41"/>
+      <c r="F11" s="35">
         <v>2067</v>
       </c>
     </row>
@@ -1632,10 +1629,10 @@
       <c r="B12" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="37"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
@@ -1731,7 +1728,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1741,26 +1738,26 @@
       <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="25" t="s">
+      <c r="B2" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="F2" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>53</v>
+      <c r="G2" s="27" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1768,21 +1765,21 @@
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="29">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28">
         <v>20</v>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="29">
         <v>1208</v>
       </c>
-      <c r="F3" s="30">
+      <c r="F3" s="29">
         <v>30</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="30">
         <f>E3*D3/2</f>
         <v>12080</v>
       </c>
@@ -1792,21 +1789,21 @@
         <v>2</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="29">
+      <c r="D4" s="28">
         <v>20</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="29">
         <v>1378</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="29">
         <v>30</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="30">
         <f t="shared" ref="G4:G5" si="0">E4*D4/2</f>
         <v>13780</v>
       </c>
@@ -1815,22 +1812,22 @@
       <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="32">
+      <c r="B5" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="31">
         <v>20</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="32">
         <v>2009</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>30</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="30">
         <f t="shared" si="0"/>
         <v>20090</v>
       </c>
@@ -1839,10 +1836,10 @@
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="35">
+      <c r="D6" s="28"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="34">
         <f>SUM(G3:G5)</f>
         <v>45950</v>
       </c>
@@ -1853,18 +1850,18 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="17"/>
       <c r="B7" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
-      <c r="E7" s="34"/>
+      <c r="E7" s="33"/>
       <c r="F7" s="22"/>
       <c r="G7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="17"/>
       <c r="B8" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -1877,7 +1874,7 @@
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
-      <c r="E9" s="26"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="23"/>
       <c r="G9" s="21"/>
     </row>
@@ -1886,21 +1883,21 @@
         <v>1</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="29">
-        <v>10</v>
-      </c>
-      <c r="E10" s="30">
+        <v>53</v>
+      </c>
+      <c r="D10" s="28">
+        <v>10</v>
+      </c>
+      <c r="E10" s="29">
         <v>1208</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="29">
         <v>30</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="30">
         <f>E10*D10/2</f>
         <v>6040</v>
       </c>
@@ -1910,21 +1907,21 @@
         <v>2</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="29">
-        <v>10</v>
-      </c>
-      <c r="E11" s="30">
+        <v>53</v>
+      </c>
+      <c r="D11" s="28">
+        <v>10</v>
+      </c>
+      <c r="E11" s="29">
         <v>1378</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="29">
         <v>30</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="30">
         <f t="shared" ref="G11:G12" si="1">E11*D11/2</f>
         <v>6890</v>
       </c>
@@ -1933,22 +1930,22 @@
       <c r="A12" s="17">
         <v>3</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>51</v>
+      <c r="B12" s="26" t="s">
+        <v>49</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="29">
-        <v>10</v>
-      </c>
-      <c r="E12" s="33">
+        <v>53</v>
+      </c>
+      <c r="D12" s="28">
+        <v>10</v>
+      </c>
+      <c r="E12" s="32">
         <v>2009</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <v>30</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="30">
         <f t="shared" si="1"/>
         <v>10045</v>
       </c>
@@ -1957,10 +1954,10 @@
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="35">
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="34">
         <f>SUM(G10:G12)</f>
         <v>22975</v>
       </c>
@@ -1971,7 +1968,7 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="17"/>
       <c r="B14" s="19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
